--- a/learn/files/hubricon-price-curve.xlsx
+++ b/learn/files/hubricon-price-curve.xlsx
@@ -2597,7 +2597,7 @@
         <v>76</v>
       </c>
       <c r="B21" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(B20),"",IF(B14&lt;&gt;"Read","The fit is not read yet: see Your history.",IF(B10&gt;=-1,"Demand this inelastic has no best price: profit rises with the price. Walk up and measure.","Too close to −1: the direction is up, the distance is unknown.")))</f>
+        <f aca="false">IF(ISNUMBER(B20),"",IF(B14&lt;&gt;"Read","The fit is not read yet: see Your history.",IF(B10&gt;=-1,"Demand this inelastic has no best price: profit rises with the price. Walk up and measure.","Too close to −1 to name a price: "&amp;IF(AND(B16&gt;0,B7&lt;1,B10&lt;-1),IF(B16/(1-B7)*B10/(1+B10)&gt;B4,"the estimate puts it above today's, so the direction is up; the distance is unknown.","the estimate puts it below today's while the range reaches −1: hold, the data cannot say which way."),"hold."))))</f>
         <v/>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
         <v>77</v>
       </c>
       <c r="B22" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(B20),IF(B20&gt;B4,"up",IF(B20&lt;B4,"down","hold")),IF(B14&lt;&gt;"Read","hold",IF(OR(B10&gt;=-1,B19="yes"),"up","hold")))</f>
+        <f aca="false">IF(ISNUMBER(B20),IF(B20&gt;B4,"up",IF(B20&lt;B4,"down","hold")),IF(B14&lt;&gt;"Read","hold",IF(B10&gt;=-1,"up",IF(AND(B19="yes",B16&gt;0,B7&lt;1),IF(B16/(1-B7)*B10/(1+B10)&gt;B4,"up","hold"),"hold"))))</f>
         <v>up</v>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
         <v/>
       </c>
       <c r="N5" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B5),ISNUMBER(G5),ISNUMBER(H5)),IF(ISNUMBER(M5),IF(M5&gt;B5,"up",IF(M5&lt;B5,"down","hold")),IF(OR(G5&gt;=-1,L5="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B5),ISNUMBER(G5),ISNUMBER(H5)),IF(ISNUMBER(M5),IF(M5&gt;B5,"up",IF(M5&lt;B5,"down","hold")),IF(G5&gt;=-1,"up",IF(AND(L5="yes",D5+F5&gt;0,E5&lt;1),IF((D5+F5)/(1-E5)*G5/(1+G5)&gt;B5,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O5" s="14" t="str">
@@ -3489,7 +3489,7 @@
         <v/>
       </c>
       <c r="N6" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B6),ISNUMBER(G6),ISNUMBER(H6)),IF(ISNUMBER(M6),IF(M6&gt;B6,"up",IF(M6&lt;B6,"down","hold")),IF(OR(G6&gt;=-1,L6="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B6),ISNUMBER(G6),ISNUMBER(H6)),IF(ISNUMBER(M6),IF(M6&gt;B6,"up",IF(M6&lt;B6,"down","hold")),IF(G6&gt;=-1,"up",IF(AND(L6="yes",D6+F6&gt;0,E6&lt;1),IF((D6+F6)/(1-E6)*G6/(1+G6)&gt;B6,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O6" s="14" t="str">
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="N7" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B7),ISNUMBER(G7),ISNUMBER(H7)),IF(ISNUMBER(M7),IF(M7&gt;B7,"up",IF(M7&lt;B7,"down","hold")),IF(OR(G7&gt;=-1,L7="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B7),ISNUMBER(G7),ISNUMBER(H7)),IF(ISNUMBER(M7),IF(M7&gt;B7,"up",IF(M7&lt;B7,"down","hold")),IF(G7&gt;=-1,"up",IF(AND(L7="yes",D7+F7&gt;0,E7&lt;1),IF((D7+F7)/(1-E7)*G7/(1+G7)&gt;B7,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O7" s="14" t="str">
@@ -3569,7 +3569,7 @@
         <v/>
       </c>
       <c r="N8" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B8),ISNUMBER(G8),ISNUMBER(H8)),IF(ISNUMBER(M8),IF(M8&gt;B8,"up",IF(M8&lt;B8,"down","hold")),IF(OR(G8&gt;=-1,L8="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B8),ISNUMBER(G8),ISNUMBER(H8)),IF(ISNUMBER(M8),IF(M8&gt;B8,"up",IF(M8&lt;B8,"down","hold")),IF(G8&gt;=-1,"up",IF(AND(L8="yes",D8+F8&gt;0,E8&lt;1),IF((D8+F8)/(1-E8)*G8/(1+G8)&gt;B8,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O8" s="14" t="str">
@@ -3609,7 +3609,7 @@
         <v/>
       </c>
       <c r="N9" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B9),ISNUMBER(G9),ISNUMBER(H9)),IF(ISNUMBER(M9),IF(M9&gt;B9,"up",IF(M9&lt;B9,"down","hold")),IF(OR(G9&gt;=-1,L9="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B9),ISNUMBER(G9),ISNUMBER(H9)),IF(ISNUMBER(M9),IF(M9&gt;B9,"up",IF(M9&lt;B9,"down","hold")),IF(G9&gt;=-1,"up",IF(AND(L9="yes",D9+F9&gt;0,E9&lt;1),IF((D9+F9)/(1-E9)*G9/(1+G9)&gt;B9,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O9" s="14" t="str">
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="N10" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B10),ISNUMBER(G10),ISNUMBER(H10)),IF(ISNUMBER(M10),IF(M10&gt;B10,"up",IF(M10&lt;B10,"down","hold")),IF(OR(G10&gt;=-1,L10="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B10),ISNUMBER(G10),ISNUMBER(H10)),IF(ISNUMBER(M10),IF(M10&gt;B10,"up",IF(M10&lt;B10,"down","hold")),IF(G10&gt;=-1,"up",IF(AND(L10="yes",D10+F10&gt;0,E10&lt;1),IF((D10+F10)/(1-E10)*G10/(1+G10)&gt;B10,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O10" s="14" t="str">
@@ -3689,7 +3689,7 @@
         <v/>
       </c>
       <c r="N11" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B11),ISNUMBER(G11),ISNUMBER(H11)),IF(ISNUMBER(M11),IF(M11&gt;B11,"up",IF(M11&lt;B11,"down","hold")),IF(OR(G11&gt;=-1,L11="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B11),ISNUMBER(G11),ISNUMBER(H11)),IF(ISNUMBER(M11),IF(M11&gt;B11,"up",IF(M11&lt;B11,"down","hold")),IF(G11&gt;=-1,"up",IF(AND(L11="yes",D11+F11&gt;0,E11&lt;1),IF((D11+F11)/(1-E11)*G11/(1+G11)&gt;B11,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O11" s="14" t="str">
@@ -3729,7 +3729,7 @@
         <v/>
       </c>
       <c r="N12" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B12),ISNUMBER(G12),ISNUMBER(H12)),IF(ISNUMBER(M12),IF(M12&gt;B12,"up",IF(M12&lt;B12,"down","hold")),IF(OR(G12&gt;=-1,L12="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B12),ISNUMBER(G12),ISNUMBER(H12)),IF(ISNUMBER(M12),IF(M12&gt;B12,"up",IF(M12&lt;B12,"down","hold")),IF(G12&gt;=-1,"up",IF(AND(L12="yes",D12+F12&gt;0,E12&lt;1),IF((D12+F12)/(1-E12)*G12/(1+G12)&gt;B12,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O12" s="14" t="str">
@@ -3769,7 +3769,7 @@
         <v/>
       </c>
       <c r="N13" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B13),ISNUMBER(G13),ISNUMBER(H13)),IF(ISNUMBER(M13),IF(M13&gt;B13,"up",IF(M13&lt;B13,"down","hold")),IF(OR(G13&gt;=-1,L13="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B13),ISNUMBER(G13),ISNUMBER(H13)),IF(ISNUMBER(M13),IF(M13&gt;B13,"up",IF(M13&lt;B13,"down","hold")),IF(G13&gt;=-1,"up",IF(AND(L13="yes",D13+F13&gt;0,E13&lt;1),IF((D13+F13)/(1-E13)*G13/(1+G13)&gt;B13,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O13" s="14" t="str">
@@ -3809,7 +3809,7 @@
         <v/>
       </c>
       <c r="N14" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B14),ISNUMBER(G14),ISNUMBER(H14)),IF(ISNUMBER(M14),IF(M14&gt;B14,"up",IF(M14&lt;B14,"down","hold")),IF(OR(G14&gt;=-1,L14="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B14),ISNUMBER(G14),ISNUMBER(H14)),IF(ISNUMBER(M14),IF(M14&gt;B14,"up",IF(M14&lt;B14,"down","hold")),IF(G14&gt;=-1,"up",IF(AND(L14="yes",D14+F14&gt;0,E14&lt;1),IF((D14+F14)/(1-E14)*G14/(1+G14)&gt;B14,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O14" s="14" t="str">
@@ -3849,7 +3849,7 @@
         <v/>
       </c>
       <c r="N15" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B15),ISNUMBER(G15),ISNUMBER(H15)),IF(ISNUMBER(M15),IF(M15&gt;B15,"up",IF(M15&lt;B15,"down","hold")),IF(OR(G15&gt;=-1,L15="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B15),ISNUMBER(G15),ISNUMBER(H15)),IF(ISNUMBER(M15),IF(M15&gt;B15,"up",IF(M15&lt;B15,"down","hold")),IF(G15&gt;=-1,"up",IF(AND(L15="yes",D15+F15&gt;0,E15&lt;1),IF((D15+F15)/(1-E15)*G15/(1+G15)&gt;B15,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O15" s="14" t="str">
@@ -3889,7 +3889,7 @@
         <v/>
       </c>
       <c r="N16" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B16),ISNUMBER(G16),ISNUMBER(H16)),IF(ISNUMBER(M16),IF(M16&gt;B16,"up",IF(M16&lt;B16,"down","hold")),IF(OR(G16&gt;=-1,L16="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B16),ISNUMBER(G16),ISNUMBER(H16)),IF(ISNUMBER(M16),IF(M16&gt;B16,"up",IF(M16&lt;B16,"down","hold")),IF(G16&gt;=-1,"up",IF(AND(L16="yes",D16+F16&gt;0,E16&lt;1),IF((D16+F16)/(1-E16)*G16/(1+G16)&gt;B16,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O16" s="14" t="str">
@@ -3929,7 +3929,7 @@
         <v/>
       </c>
       <c r="N17" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B17),ISNUMBER(G17),ISNUMBER(H17)),IF(ISNUMBER(M17),IF(M17&gt;B17,"up",IF(M17&lt;B17,"down","hold")),IF(OR(G17&gt;=-1,L17="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B17),ISNUMBER(G17),ISNUMBER(H17)),IF(ISNUMBER(M17),IF(M17&gt;B17,"up",IF(M17&lt;B17,"down","hold")),IF(G17&gt;=-1,"up",IF(AND(L17="yes",D17+F17&gt;0,E17&lt;1),IF((D17+F17)/(1-E17)*G17/(1+G17)&gt;B17,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O17" s="14" t="str">
@@ -3969,7 +3969,7 @@
         <v/>
       </c>
       <c r="N18" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B18),ISNUMBER(G18),ISNUMBER(H18)),IF(ISNUMBER(M18),IF(M18&gt;B18,"up",IF(M18&lt;B18,"down","hold")),IF(OR(G18&gt;=-1,L18="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B18),ISNUMBER(G18),ISNUMBER(H18)),IF(ISNUMBER(M18),IF(M18&gt;B18,"up",IF(M18&lt;B18,"down","hold")),IF(G18&gt;=-1,"up",IF(AND(L18="yes",D18+F18&gt;0,E18&lt;1),IF((D18+F18)/(1-E18)*G18/(1+G18)&gt;B18,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O18" s="14" t="str">
@@ -4009,7 +4009,7 @@
         <v/>
       </c>
       <c r="N19" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B19),ISNUMBER(G19),ISNUMBER(H19)),IF(ISNUMBER(M19),IF(M19&gt;B19,"up",IF(M19&lt;B19,"down","hold")),IF(OR(G19&gt;=-1,L19="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B19),ISNUMBER(G19),ISNUMBER(H19)),IF(ISNUMBER(M19),IF(M19&gt;B19,"up",IF(M19&lt;B19,"down","hold")),IF(G19&gt;=-1,"up",IF(AND(L19="yes",D19+F19&gt;0,E19&lt;1),IF((D19+F19)/(1-E19)*G19/(1+G19)&gt;B19,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O19" s="14" t="str">
@@ -4049,7 +4049,7 @@
         <v/>
       </c>
       <c r="N20" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B20),ISNUMBER(G20),ISNUMBER(H20)),IF(ISNUMBER(M20),IF(M20&gt;B20,"up",IF(M20&lt;B20,"down","hold")),IF(OR(G20&gt;=-1,L20="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B20),ISNUMBER(G20),ISNUMBER(H20)),IF(ISNUMBER(M20),IF(M20&gt;B20,"up",IF(M20&lt;B20,"down","hold")),IF(G20&gt;=-1,"up",IF(AND(L20="yes",D20+F20&gt;0,E20&lt;1),IF((D20+F20)/(1-E20)*G20/(1+G20)&gt;B20,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O20" s="14" t="str">
@@ -4089,7 +4089,7 @@
         <v/>
       </c>
       <c r="N21" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B21),ISNUMBER(G21),ISNUMBER(H21)),IF(ISNUMBER(M21),IF(M21&gt;B21,"up",IF(M21&lt;B21,"down","hold")),IF(OR(G21&gt;=-1,L21="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B21),ISNUMBER(G21),ISNUMBER(H21)),IF(ISNUMBER(M21),IF(M21&gt;B21,"up",IF(M21&lt;B21,"down","hold")),IF(G21&gt;=-1,"up",IF(AND(L21="yes",D21+F21&gt;0,E21&lt;1),IF((D21+F21)/(1-E21)*G21/(1+G21)&gt;B21,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O21" s="14" t="str">
@@ -4129,7 +4129,7 @@
         <v/>
       </c>
       <c r="N22" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B22),ISNUMBER(G22),ISNUMBER(H22)),IF(ISNUMBER(M22),IF(M22&gt;B22,"up",IF(M22&lt;B22,"down","hold")),IF(OR(G22&gt;=-1,L22="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B22),ISNUMBER(G22),ISNUMBER(H22)),IF(ISNUMBER(M22),IF(M22&gt;B22,"up",IF(M22&lt;B22,"down","hold")),IF(G22&gt;=-1,"up",IF(AND(L22="yes",D22+F22&gt;0,E22&lt;1),IF((D22+F22)/(1-E22)*G22/(1+G22)&gt;B22,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O22" s="14" t="str">
@@ -4169,7 +4169,7 @@
         <v/>
       </c>
       <c r="N23" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B23),ISNUMBER(G23),ISNUMBER(H23)),IF(ISNUMBER(M23),IF(M23&gt;B23,"up",IF(M23&lt;B23,"down","hold")),IF(OR(G23&gt;=-1,L23="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B23),ISNUMBER(G23),ISNUMBER(H23)),IF(ISNUMBER(M23),IF(M23&gt;B23,"up",IF(M23&lt;B23,"down","hold")),IF(G23&gt;=-1,"up",IF(AND(L23="yes",D23+F23&gt;0,E23&lt;1),IF((D23+F23)/(1-E23)*G23/(1+G23)&gt;B23,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O23" s="14" t="str">
@@ -4209,7 +4209,7 @@
         <v/>
       </c>
       <c r="N24" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B24),ISNUMBER(G24),ISNUMBER(H24)),IF(ISNUMBER(M24),IF(M24&gt;B24,"up",IF(M24&lt;B24,"down","hold")),IF(OR(G24&gt;=-1,L24="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B24),ISNUMBER(G24),ISNUMBER(H24)),IF(ISNUMBER(M24),IF(M24&gt;B24,"up",IF(M24&lt;B24,"down","hold")),IF(G24&gt;=-1,"up",IF(AND(L24="yes",D24+F24&gt;0,E24&lt;1),IF((D24+F24)/(1-E24)*G24/(1+G24)&gt;B24,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O24" s="14" t="str">
@@ -4249,7 +4249,7 @@
         <v/>
       </c>
       <c r="N25" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B25),ISNUMBER(G25),ISNUMBER(H25)),IF(ISNUMBER(M25),IF(M25&gt;B25,"up",IF(M25&lt;B25,"down","hold")),IF(OR(G25&gt;=-1,L25="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B25),ISNUMBER(G25),ISNUMBER(H25)),IF(ISNUMBER(M25),IF(M25&gt;B25,"up",IF(M25&lt;B25,"down","hold")),IF(G25&gt;=-1,"up",IF(AND(L25="yes",D25+F25&gt;0,E25&lt;1),IF((D25+F25)/(1-E25)*G25/(1+G25)&gt;B25,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O25" s="14" t="str">
@@ -4289,7 +4289,7 @@
         <v/>
       </c>
       <c r="N26" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B26),ISNUMBER(G26),ISNUMBER(H26)),IF(ISNUMBER(M26),IF(M26&gt;B26,"up",IF(M26&lt;B26,"down","hold")),IF(OR(G26&gt;=-1,L26="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B26),ISNUMBER(G26),ISNUMBER(H26)),IF(ISNUMBER(M26),IF(M26&gt;B26,"up",IF(M26&lt;B26,"down","hold")),IF(G26&gt;=-1,"up",IF(AND(L26="yes",D26+F26&gt;0,E26&lt;1),IF((D26+F26)/(1-E26)*G26/(1+G26)&gt;B26,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O26" s="14" t="str">
@@ -4329,7 +4329,7 @@
         <v/>
       </c>
       <c r="N27" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B27),ISNUMBER(G27),ISNUMBER(H27)),IF(ISNUMBER(M27),IF(M27&gt;B27,"up",IF(M27&lt;B27,"down","hold")),IF(OR(G27&gt;=-1,L27="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B27),ISNUMBER(G27),ISNUMBER(H27)),IF(ISNUMBER(M27),IF(M27&gt;B27,"up",IF(M27&lt;B27,"down","hold")),IF(G27&gt;=-1,"up",IF(AND(L27="yes",D27+F27&gt;0,E27&lt;1),IF((D27+F27)/(1-E27)*G27/(1+G27)&gt;B27,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O27" s="14" t="str">
@@ -4369,7 +4369,7 @@
         <v/>
       </c>
       <c r="N28" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B28),ISNUMBER(G28),ISNUMBER(H28)),IF(ISNUMBER(M28),IF(M28&gt;B28,"up",IF(M28&lt;B28,"down","hold")),IF(OR(G28&gt;=-1,L28="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B28),ISNUMBER(G28),ISNUMBER(H28)),IF(ISNUMBER(M28),IF(M28&gt;B28,"up",IF(M28&lt;B28,"down","hold")),IF(G28&gt;=-1,"up",IF(AND(L28="yes",D28+F28&gt;0,E28&lt;1),IF((D28+F28)/(1-E28)*G28/(1+G28)&gt;B28,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O28" s="14" t="str">
@@ -4409,7 +4409,7 @@
         <v/>
       </c>
       <c r="N29" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B29),ISNUMBER(G29),ISNUMBER(H29)),IF(ISNUMBER(M29),IF(M29&gt;B29,"up",IF(M29&lt;B29,"down","hold")),IF(OR(G29&gt;=-1,L29="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B29),ISNUMBER(G29),ISNUMBER(H29)),IF(ISNUMBER(M29),IF(M29&gt;B29,"up",IF(M29&lt;B29,"down","hold")),IF(G29&gt;=-1,"up",IF(AND(L29="yes",D29+F29&gt;0,E29&lt;1),IF((D29+F29)/(1-E29)*G29/(1+G29)&gt;B29,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O29" s="14" t="str">
@@ -4449,7 +4449,7 @@
         <v/>
       </c>
       <c r="N30" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B30),ISNUMBER(G30),ISNUMBER(H30)),IF(ISNUMBER(M30),IF(M30&gt;B30,"up",IF(M30&lt;B30,"down","hold")),IF(OR(G30&gt;=-1,L30="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B30),ISNUMBER(G30),ISNUMBER(H30)),IF(ISNUMBER(M30),IF(M30&gt;B30,"up",IF(M30&lt;B30,"down","hold")),IF(G30&gt;=-1,"up",IF(AND(L30="yes",D30+F30&gt;0,E30&lt;1),IF((D30+F30)/(1-E30)*G30/(1+G30)&gt;B30,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O30" s="14" t="str">
@@ -4489,7 +4489,7 @@
         <v/>
       </c>
       <c r="N31" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B31),ISNUMBER(G31),ISNUMBER(H31)),IF(ISNUMBER(M31),IF(M31&gt;B31,"up",IF(M31&lt;B31,"down","hold")),IF(OR(G31&gt;=-1,L31="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B31),ISNUMBER(G31),ISNUMBER(H31)),IF(ISNUMBER(M31),IF(M31&gt;B31,"up",IF(M31&lt;B31,"down","hold")),IF(G31&gt;=-1,"up",IF(AND(L31="yes",D31+F31&gt;0,E31&lt;1),IF((D31+F31)/(1-E31)*G31/(1+G31)&gt;B31,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O31" s="14" t="str">
@@ -4529,7 +4529,7 @@
         <v/>
       </c>
       <c r="N32" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B32),ISNUMBER(G32),ISNUMBER(H32)),IF(ISNUMBER(M32),IF(M32&gt;B32,"up",IF(M32&lt;B32,"down","hold")),IF(OR(G32&gt;=-1,L32="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B32),ISNUMBER(G32),ISNUMBER(H32)),IF(ISNUMBER(M32),IF(M32&gt;B32,"up",IF(M32&lt;B32,"down","hold")),IF(G32&gt;=-1,"up",IF(AND(L32="yes",D32+F32&gt;0,E32&lt;1),IF((D32+F32)/(1-E32)*G32/(1+G32)&gt;B32,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O32" s="14" t="str">
@@ -4569,7 +4569,7 @@
         <v/>
       </c>
       <c r="N33" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B33),ISNUMBER(G33),ISNUMBER(H33)),IF(ISNUMBER(M33),IF(M33&gt;B33,"up",IF(M33&lt;B33,"down","hold")),IF(OR(G33&gt;=-1,L33="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B33),ISNUMBER(G33),ISNUMBER(H33)),IF(ISNUMBER(M33),IF(M33&gt;B33,"up",IF(M33&lt;B33,"down","hold")),IF(G33&gt;=-1,"up",IF(AND(L33="yes",D33+F33&gt;0,E33&lt;1),IF((D33+F33)/(1-E33)*G33/(1+G33)&gt;B33,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O33" s="14" t="str">
@@ -4609,7 +4609,7 @@
         <v/>
       </c>
       <c r="N34" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B34),ISNUMBER(G34),ISNUMBER(H34)),IF(ISNUMBER(M34),IF(M34&gt;B34,"up",IF(M34&lt;B34,"down","hold")),IF(OR(G34&gt;=-1,L34="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B34),ISNUMBER(G34),ISNUMBER(H34)),IF(ISNUMBER(M34),IF(M34&gt;B34,"up",IF(M34&lt;B34,"down","hold")),IF(G34&gt;=-1,"up",IF(AND(L34="yes",D34+F34&gt;0,E34&lt;1),IF((D34+F34)/(1-E34)*G34/(1+G34)&gt;B34,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O34" s="14" t="str">
@@ -4649,7 +4649,7 @@
         <v/>
       </c>
       <c r="N35" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B35),ISNUMBER(G35),ISNUMBER(H35)),IF(ISNUMBER(M35),IF(M35&gt;B35,"up",IF(M35&lt;B35,"down","hold")),IF(OR(G35&gt;=-1,L35="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B35),ISNUMBER(G35),ISNUMBER(H35)),IF(ISNUMBER(M35),IF(M35&gt;B35,"up",IF(M35&lt;B35,"down","hold")),IF(G35&gt;=-1,"up",IF(AND(L35="yes",D35+F35&gt;0,E35&lt;1),IF((D35+F35)/(1-E35)*G35/(1+G35)&gt;B35,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O35" s="14" t="str">
@@ -4689,7 +4689,7 @@
         <v/>
       </c>
       <c r="N36" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B36),ISNUMBER(G36),ISNUMBER(H36)),IF(ISNUMBER(M36),IF(M36&gt;B36,"up",IF(M36&lt;B36,"down","hold")),IF(OR(G36&gt;=-1,L36="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B36),ISNUMBER(G36),ISNUMBER(H36)),IF(ISNUMBER(M36),IF(M36&gt;B36,"up",IF(M36&lt;B36,"down","hold")),IF(G36&gt;=-1,"up",IF(AND(L36="yes",D36+F36&gt;0,E36&lt;1),IF((D36+F36)/(1-E36)*G36/(1+G36)&gt;B36,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O36" s="14" t="str">
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="N37" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B37),ISNUMBER(G37),ISNUMBER(H37)),IF(ISNUMBER(M37),IF(M37&gt;B37,"up",IF(M37&lt;B37,"down","hold")),IF(OR(G37&gt;=-1,L37="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B37),ISNUMBER(G37),ISNUMBER(H37)),IF(ISNUMBER(M37),IF(M37&gt;B37,"up",IF(M37&lt;B37,"down","hold")),IF(G37&gt;=-1,"up",IF(AND(L37="yes",D37+F37&gt;0,E37&lt;1),IF((D37+F37)/(1-E37)*G37/(1+G37)&gt;B37,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O37" s="14" t="str">
@@ -4769,7 +4769,7 @@
         <v/>
       </c>
       <c r="N38" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B38),ISNUMBER(G38),ISNUMBER(H38)),IF(ISNUMBER(M38),IF(M38&gt;B38,"up",IF(M38&lt;B38,"down","hold")),IF(OR(G38&gt;=-1,L38="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B38),ISNUMBER(G38),ISNUMBER(H38)),IF(ISNUMBER(M38),IF(M38&gt;B38,"up",IF(M38&lt;B38,"down","hold")),IF(G38&gt;=-1,"up",IF(AND(L38="yes",D38+F38&gt;0,E38&lt;1),IF((D38+F38)/(1-E38)*G38/(1+G38)&gt;B38,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O38" s="14" t="str">
@@ -4809,7 +4809,7 @@
         <v/>
       </c>
       <c r="N39" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B39),ISNUMBER(G39),ISNUMBER(H39)),IF(ISNUMBER(M39),IF(M39&gt;B39,"up",IF(M39&lt;B39,"down","hold")),IF(OR(G39&gt;=-1,L39="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B39),ISNUMBER(G39),ISNUMBER(H39)),IF(ISNUMBER(M39),IF(M39&gt;B39,"up",IF(M39&lt;B39,"down","hold")),IF(G39&gt;=-1,"up",IF(AND(L39="yes",D39+F39&gt;0,E39&lt;1),IF((D39+F39)/(1-E39)*G39/(1+G39)&gt;B39,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O39" s="14" t="str">
@@ -4849,7 +4849,7 @@
         <v/>
       </c>
       <c r="N40" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B40),ISNUMBER(G40),ISNUMBER(H40)),IF(ISNUMBER(M40),IF(M40&gt;B40,"up",IF(M40&lt;B40,"down","hold")),IF(OR(G40&gt;=-1,L40="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B40),ISNUMBER(G40),ISNUMBER(H40)),IF(ISNUMBER(M40),IF(M40&gt;B40,"up",IF(M40&lt;B40,"down","hold")),IF(G40&gt;=-1,"up",IF(AND(L40="yes",D40+F40&gt;0,E40&lt;1),IF((D40+F40)/(1-E40)*G40/(1+G40)&gt;B40,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O40" s="14" t="str">
@@ -4889,7 +4889,7 @@
         <v/>
       </c>
       <c r="N41" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B41),ISNUMBER(G41),ISNUMBER(H41)),IF(ISNUMBER(M41),IF(M41&gt;B41,"up",IF(M41&lt;B41,"down","hold")),IF(OR(G41&gt;=-1,L41="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B41),ISNUMBER(G41),ISNUMBER(H41)),IF(ISNUMBER(M41),IF(M41&gt;B41,"up",IF(M41&lt;B41,"down","hold")),IF(G41&gt;=-1,"up",IF(AND(L41="yes",D41+F41&gt;0,E41&lt;1),IF((D41+F41)/(1-E41)*G41/(1+G41)&gt;B41,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O41" s="14" t="str">
@@ -4929,7 +4929,7 @@
         <v/>
       </c>
       <c r="N42" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B42),ISNUMBER(G42),ISNUMBER(H42)),IF(ISNUMBER(M42),IF(M42&gt;B42,"up",IF(M42&lt;B42,"down","hold")),IF(OR(G42&gt;=-1,L42="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B42),ISNUMBER(G42),ISNUMBER(H42)),IF(ISNUMBER(M42),IF(M42&gt;B42,"up",IF(M42&lt;B42,"down","hold")),IF(G42&gt;=-1,"up",IF(AND(L42="yes",D42+F42&gt;0,E42&lt;1),IF((D42+F42)/(1-E42)*G42/(1+G42)&gt;B42,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O42" s="14" t="str">
@@ -4969,7 +4969,7 @@
         <v/>
       </c>
       <c r="N43" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B43),ISNUMBER(G43),ISNUMBER(H43)),IF(ISNUMBER(M43),IF(M43&gt;B43,"up",IF(M43&lt;B43,"down","hold")),IF(OR(G43&gt;=-1,L43="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B43),ISNUMBER(G43),ISNUMBER(H43)),IF(ISNUMBER(M43),IF(M43&gt;B43,"up",IF(M43&lt;B43,"down","hold")),IF(G43&gt;=-1,"up",IF(AND(L43="yes",D43+F43&gt;0,E43&lt;1),IF((D43+F43)/(1-E43)*G43/(1+G43)&gt;B43,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O43" s="14" t="str">
@@ -5009,7 +5009,7 @@
         <v/>
       </c>
       <c r="N44" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B44),ISNUMBER(G44),ISNUMBER(H44)),IF(ISNUMBER(M44),IF(M44&gt;B44,"up",IF(M44&lt;B44,"down","hold")),IF(OR(G44&gt;=-1,L44="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B44),ISNUMBER(G44),ISNUMBER(H44)),IF(ISNUMBER(M44),IF(M44&gt;B44,"up",IF(M44&lt;B44,"down","hold")),IF(G44&gt;=-1,"up",IF(AND(L44="yes",D44+F44&gt;0,E44&lt;1),IF((D44+F44)/(1-E44)*G44/(1+G44)&gt;B44,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O44" s="14" t="str">
@@ -5049,7 +5049,7 @@
         <v/>
       </c>
       <c r="N45" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B45),ISNUMBER(G45),ISNUMBER(H45)),IF(ISNUMBER(M45),IF(M45&gt;B45,"up",IF(M45&lt;B45,"down","hold")),IF(OR(G45&gt;=-1,L45="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B45),ISNUMBER(G45),ISNUMBER(H45)),IF(ISNUMBER(M45),IF(M45&gt;B45,"up",IF(M45&lt;B45,"down","hold")),IF(G45&gt;=-1,"up",IF(AND(L45="yes",D45+F45&gt;0,E45&lt;1),IF((D45+F45)/(1-E45)*G45/(1+G45)&gt;B45,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O45" s="14" t="str">
@@ -5089,7 +5089,7 @@
         <v/>
       </c>
       <c r="N46" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B46),ISNUMBER(G46),ISNUMBER(H46)),IF(ISNUMBER(M46),IF(M46&gt;B46,"up",IF(M46&lt;B46,"down","hold")),IF(OR(G46&gt;=-1,L46="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B46),ISNUMBER(G46),ISNUMBER(H46)),IF(ISNUMBER(M46),IF(M46&gt;B46,"up",IF(M46&lt;B46,"down","hold")),IF(G46&gt;=-1,"up",IF(AND(L46="yes",D46+F46&gt;0,E46&lt;1),IF((D46+F46)/(1-E46)*G46/(1+G46)&gt;B46,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O46" s="14" t="str">
@@ -5129,7 +5129,7 @@
         <v/>
       </c>
       <c r="N47" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B47),ISNUMBER(G47),ISNUMBER(H47)),IF(ISNUMBER(M47),IF(M47&gt;B47,"up",IF(M47&lt;B47,"down","hold")),IF(OR(G47&gt;=-1,L47="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B47),ISNUMBER(G47),ISNUMBER(H47)),IF(ISNUMBER(M47),IF(M47&gt;B47,"up",IF(M47&lt;B47,"down","hold")),IF(G47&gt;=-1,"up",IF(AND(L47="yes",D47+F47&gt;0,E47&lt;1),IF((D47+F47)/(1-E47)*G47/(1+G47)&gt;B47,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O47" s="14" t="str">
@@ -5169,7 +5169,7 @@
         <v/>
       </c>
       <c r="N48" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B48),ISNUMBER(G48),ISNUMBER(H48)),IF(ISNUMBER(M48),IF(M48&gt;B48,"up",IF(M48&lt;B48,"down","hold")),IF(OR(G48&gt;=-1,L48="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B48),ISNUMBER(G48),ISNUMBER(H48)),IF(ISNUMBER(M48),IF(M48&gt;B48,"up",IF(M48&lt;B48,"down","hold")),IF(G48&gt;=-1,"up",IF(AND(L48="yes",D48+F48&gt;0,E48&lt;1),IF((D48+F48)/(1-E48)*G48/(1+G48)&gt;B48,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O48" s="14" t="str">
@@ -5209,7 +5209,7 @@
         <v/>
       </c>
       <c r="N49" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B49),ISNUMBER(G49),ISNUMBER(H49)),IF(ISNUMBER(M49),IF(M49&gt;B49,"up",IF(M49&lt;B49,"down","hold")),IF(OR(G49&gt;=-1,L49="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B49),ISNUMBER(G49),ISNUMBER(H49)),IF(ISNUMBER(M49),IF(M49&gt;B49,"up",IF(M49&lt;B49,"down","hold")),IF(G49&gt;=-1,"up",IF(AND(L49="yes",D49+F49&gt;0,E49&lt;1),IF((D49+F49)/(1-E49)*G49/(1+G49)&gt;B49,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O49" s="14" t="str">
@@ -5249,7 +5249,7 @@
         <v/>
       </c>
       <c r="N50" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B50),ISNUMBER(G50),ISNUMBER(H50)),IF(ISNUMBER(M50),IF(M50&gt;B50,"up",IF(M50&lt;B50,"down","hold")),IF(OR(G50&gt;=-1,L50="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B50),ISNUMBER(G50),ISNUMBER(H50)),IF(ISNUMBER(M50),IF(M50&gt;B50,"up",IF(M50&lt;B50,"down","hold")),IF(G50&gt;=-1,"up",IF(AND(L50="yes",D50+F50&gt;0,E50&lt;1),IF((D50+F50)/(1-E50)*G50/(1+G50)&gt;B50,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O50" s="14" t="str">
@@ -5289,7 +5289,7 @@
         <v/>
       </c>
       <c r="N51" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B51),ISNUMBER(G51),ISNUMBER(H51)),IF(ISNUMBER(M51),IF(M51&gt;B51,"up",IF(M51&lt;B51,"down","hold")),IF(OR(G51&gt;=-1,L51="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B51),ISNUMBER(G51),ISNUMBER(H51)),IF(ISNUMBER(M51),IF(M51&gt;B51,"up",IF(M51&lt;B51,"down","hold")),IF(G51&gt;=-1,"up",IF(AND(L51="yes",D51+F51&gt;0,E51&lt;1),IF((D51+F51)/(1-E51)*G51/(1+G51)&gt;B51,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O51" s="14" t="str">
@@ -5329,7 +5329,7 @@
         <v/>
       </c>
       <c r="N52" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B52),ISNUMBER(G52),ISNUMBER(H52)),IF(ISNUMBER(M52),IF(M52&gt;B52,"up",IF(M52&lt;B52,"down","hold")),IF(OR(G52&gt;=-1,L52="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B52),ISNUMBER(G52),ISNUMBER(H52)),IF(ISNUMBER(M52),IF(M52&gt;B52,"up",IF(M52&lt;B52,"down","hold")),IF(G52&gt;=-1,"up",IF(AND(L52="yes",D52+F52&gt;0,E52&lt;1),IF((D52+F52)/(1-E52)*G52/(1+G52)&gt;B52,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O52" s="14" t="str">
@@ -5369,7 +5369,7 @@
         <v/>
       </c>
       <c r="N53" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B53),ISNUMBER(G53),ISNUMBER(H53)),IF(ISNUMBER(M53),IF(M53&gt;B53,"up",IF(M53&lt;B53,"down","hold")),IF(OR(G53&gt;=-1,L53="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B53),ISNUMBER(G53),ISNUMBER(H53)),IF(ISNUMBER(M53),IF(M53&gt;B53,"up",IF(M53&lt;B53,"down","hold")),IF(G53&gt;=-1,"up",IF(AND(L53="yes",D53+F53&gt;0,E53&lt;1),IF((D53+F53)/(1-E53)*G53/(1+G53)&gt;B53,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O53" s="14" t="str">
@@ -5409,7 +5409,7 @@
         <v/>
       </c>
       <c r="N54" s="2" t="str">
-        <f aca="false">IF(AND(ISNUMBER(B54),ISNUMBER(G54),ISNUMBER(H54)),IF(ISNUMBER(M54),IF(M54&gt;B54,"up",IF(M54&lt;B54,"down","hold")),IF(OR(G54&gt;=-1,L54="yes"),"up","hold")),"")</f>
+        <f aca="false">IF(AND(ISNUMBER(B54),ISNUMBER(G54),ISNUMBER(H54)),IF(ISNUMBER(M54),IF(M54&gt;B54,"up",IF(M54&lt;B54,"down","hold")),IF(G54&gt;=-1,"up",IF(AND(L54="yes",D54+F54&gt;0,E54&lt;1),IF((D54+F54)/(1-E54)*G54/(1+G54)&gt;B54,"up","hold"),"hold"))),"")</f>
         <v/>
       </c>
       <c r="O54" s="14" t="str">
